--- a/production/watch-CHECKED/Manufacturing/Assembly/ZSWatch-Watch-bom.xlsx
+++ b/production/watch-CHECKED/Manufacturing/Assembly/ZSWatch-Watch-bom.xlsx
@@ -1061,7 +1061,7 @@
     <t>Created:</t>
   </si>
   <si>
-    <t>2026-02-20 19:32:44</t>
+    <t>2026-02-21 13:11:34</t>
   </si>
   <si>
     <t>KiCost® v1.1.20 + KiBot v1.8.5</t>
